--- a/auswertung/ergebnisse/teilstudie_b/roi_modell.xlsx
+++ b/auswertung/ergebnisse/teilstudie_b/roi_modell.xlsx
@@ -569,7 +569,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Erzeugt mit auswertung/teilstudie_b.py am 2026-10-21T06:51:17+00:00; Git-Stand 09d00f859c16 (nicht committete Änderungen).</t>
+          <t>Erzeugt mit auswertung/teilstudie_b.py am 2026-10-26T19:06:00+00:00; Git-Stand 038c291f34cd (nicht committete Änderungen).</t>
         </is>
       </c>
     </row>
